--- a/public/plantillas/Template_Carga_Masiva_POI.xlsx
+++ b/public/plantillas/Template_Carga_Masiva_POI.xlsx
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\FrontendGoreSM\frontend-dashboardgoresm\public\plantillas\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB501670-42EE-40FE-BC9E-27BDB35C379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A815224F-3726-4E80-AB90-02081EDBAE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19575" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POI_Por_ActividadOperativaAnual" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">POI_Por_ActividadOperativaAnual!$A$2:$JR$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">POI_Por_ActividadOperativaAnual!$A$2:$JS$3</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="349">
   <si>
     <t>POI</t>
   </si>
@@ -1064,6 +1064,12 @@
   </si>
   <si>
     <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>Periodo</t>
+  </si>
+  <si>
+    <t>2023-2026</t>
   </si>
 </sst>
 </file>
@@ -1437,1144 +1443,1150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:JR3"/>
+  <dimension ref="A2:JS3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" customWidth="1"/>
-    <col min="17" max="19" width="12.7109375" customWidth="1"/>
-    <col min="20" max="20" width="18.7109375" customWidth="1"/>
-    <col min="21" max="22" width="12.7109375" customWidth="1"/>
-    <col min="23" max="23" width="18.7109375" customWidth="1"/>
-    <col min="24" max="26" width="12.7109375" customWidth="1"/>
-    <col min="27" max="27" width="18.7109375" customWidth="1"/>
-    <col min="28" max="29" width="12.7109375" customWidth="1"/>
-    <col min="30" max="30" width="26.7109375" customWidth="1"/>
-    <col min="31" max="33" width="12.7109375" customWidth="1"/>
-    <col min="34" max="34" width="18.7109375" customWidth="1"/>
-    <col min="35" max="36" width="12.7109375" customWidth="1"/>
-    <col min="37" max="37" width="26.7109375" customWidth="1"/>
-    <col min="38" max="42" width="12.7109375" customWidth="1"/>
-    <col min="43" max="43" width="18.7109375" customWidth="1"/>
-    <col min="44" max="50" width="12.7109375" customWidth="1"/>
-    <col min="51" max="53" width="18.7109375" customWidth="1"/>
-    <col min="54" max="55" width="12.7109375" customWidth="1"/>
-    <col min="56" max="60" width="18.7109375" customWidth="1"/>
-    <col min="61" max="62" width="26.7109375" customWidth="1"/>
-    <col min="63" max="64" width="12.7109375" customWidth="1"/>
-    <col min="65" max="65" width="18.7109375" customWidth="1"/>
-    <col min="66" max="68" width="12.7109375" customWidth="1"/>
-    <col min="69" max="69" width="18.7109375" customWidth="1"/>
-    <col min="70" max="74" width="12.7109375" customWidth="1"/>
-    <col min="75" max="75" width="26.7109375" customWidth="1"/>
-    <col min="76" max="76" width="12.7109375" customWidth="1"/>
-    <col min="77" max="77" width="18.7109375" customWidth="1"/>
-    <col min="78" max="78" width="12.7109375" customWidth="1"/>
-    <col min="79" max="81" width="18.7109375" customWidth="1"/>
-    <col min="82" max="278" width="12.7109375" customWidth="1"/>
+    <col min="2" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="40" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" customWidth="1"/>
+    <col min="13" max="16" width="12.7109375" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" customWidth="1"/>
+    <col min="18" max="20" width="12.7109375" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" customWidth="1"/>
+    <col min="22" max="23" width="12.7109375" customWidth="1"/>
+    <col min="24" max="24" width="18.7109375" customWidth="1"/>
+    <col min="25" max="27" width="12.7109375" customWidth="1"/>
+    <col min="28" max="28" width="18.7109375" customWidth="1"/>
+    <col min="29" max="30" width="12.7109375" customWidth="1"/>
+    <col min="31" max="31" width="26.7109375" customWidth="1"/>
+    <col min="32" max="34" width="12.7109375" customWidth="1"/>
+    <col min="35" max="35" width="18.7109375" customWidth="1"/>
+    <col min="36" max="37" width="12.7109375" customWidth="1"/>
+    <col min="38" max="38" width="26.7109375" customWidth="1"/>
+    <col min="39" max="43" width="12.7109375" customWidth="1"/>
+    <col min="44" max="44" width="18.7109375" customWidth="1"/>
+    <col min="45" max="51" width="12.7109375" customWidth="1"/>
+    <col min="52" max="54" width="18.7109375" customWidth="1"/>
+    <col min="55" max="56" width="12.7109375" customWidth="1"/>
+    <col min="57" max="61" width="18.7109375" customWidth="1"/>
+    <col min="62" max="63" width="26.7109375" customWidth="1"/>
+    <col min="64" max="65" width="12.7109375" customWidth="1"/>
+    <col min="66" max="66" width="18.7109375" customWidth="1"/>
+    <col min="67" max="69" width="12.7109375" customWidth="1"/>
+    <col min="70" max="70" width="18.7109375" customWidth="1"/>
+    <col min="71" max="75" width="12.7109375" customWidth="1"/>
+    <col min="76" max="76" width="26.7109375" customWidth="1"/>
+    <col min="77" max="77" width="12.7109375" customWidth="1"/>
+    <col min="78" max="78" width="18.7109375" customWidth="1"/>
+    <col min="79" max="79" width="12.7109375" customWidth="1"/>
+    <col min="80" max="82" width="18.7109375" customWidth="1"/>
+    <col min="83" max="279" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:278" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:279" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BP2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BQ2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BR2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BU2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="BV2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BV2" s="1" t="s">
+      <c r="BW2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BX2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="BY2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="DF2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="DF2" s="1" t="s">
+      <c r="DG2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="DG2" s="1" t="s">
+      <c r="DH2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="DH2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="DI2" s="1" t="s">
+      <c r="DJ2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="DJ2" s="1" t="s">
+      <c r="DK2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="DK2" s="1" t="s">
+      <c r="DL2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="DL2" s="1" t="s">
+      <c r="DM2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="DM2" s="1" t="s">
+      <c r="DN2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="DN2" s="1" t="s">
+      <c r="DO2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="DO2" s="1" t="s">
+      <c r="DP2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DP2" s="1" t="s">
+      <c r="DQ2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="DQ2" s="1" t="s">
+      <c r="DR2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="DR2" s="1" t="s">
+      <c r="DS2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="DS2" s="1" t="s">
+      <c r="DT2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="DT2" s="1" t="s">
+      <c r="DU2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="DU2" s="1" t="s">
+      <c r="DV2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="DV2" s="1" t="s">
+      <c r="DW2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="DW2" s="1" t="s">
+      <c r="DX2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="DX2" s="1" t="s">
+      <c r="DY2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="DY2" s="1" t="s">
+      <c r="DZ2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="DZ2" s="1" t="s">
+      <c r="EA2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="EA2" s="1" t="s">
+      <c r="EB2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="EB2" s="1" t="s">
+      <c r="EC2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="EC2" s="1" t="s">
+      <c r="ED2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="ED2" s="1" t="s">
+      <c r="EE2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="EE2" s="1" t="s">
+      <c r="EF2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="EF2" s="1" t="s">
+      <c r="EG2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="EG2" s="1" t="s">
+      <c r="EH2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="EH2" s="1" t="s">
+      <c r="EI2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="EI2" s="1" t="s">
+      <c r="EJ2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="EJ2" s="1" t="s">
+      <c r="EK2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="EK2" s="1" t="s">
+      <c r="EL2" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="EL2" s="1" t="s">
+      <c r="EM2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="EM2" s="1" t="s">
+      <c r="EN2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="EN2" s="1" t="s">
+      <c r="EO2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="EO2" s="1" t="s">
+      <c r="EP2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="EP2" s="1" t="s">
+      <c r="EQ2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="EQ2" s="1" t="s">
+      <c r="ER2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="ER2" s="1" t="s">
+      <c r="ES2" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="ES2" s="1" t="s">
+      <c r="ET2" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="ET2" s="1" t="s">
+      <c r="EU2" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="EU2" s="1" t="s">
+      <c r="EV2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="EV2" s="1" t="s">
+      <c r="EW2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="EW2" s="1" t="s">
+      <c r="EX2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="EX2" s="1" t="s">
+      <c r="EY2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="EY2" s="1" t="s">
+      <c r="EZ2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="EZ2" s="1" t="s">
+      <c r="FA2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="FA2" s="1" t="s">
+      <c r="FB2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="FB2" s="1" t="s">
+      <c r="FC2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="FC2" s="1" t="s">
+      <c r="FD2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="FD2" s="1" t="s">
+      <c r="FE2" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="FE2" s="1" t="s">
+      <c r="FF2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="FF2" s="1" t="s">
+      <c r="FG2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="FG2" s="1" t="s">
+      <c r="FH2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="FH2" s="1" t="s">
+      <c r="FI2" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="FI2" s="1" t="s">
+      <c r="FJ2" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="FJ2" s="1" t="s">
+      <c r="FK2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="FK2" s="1" t="s">
+      <c r="FL2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="FL2" s="1" t="s">
+      <c r="FM2" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="FM2" s="1" t="s">
+      <c r="FN2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="FN2" s="1" t="s">
+      <c r="FO2" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="FO2" s="1" t="s">
+      <c r="FP2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="FP2" s="1" t="s">
+      <c r="FQ2" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="FQ2" s="1" t="s">
+      <c r="FR2" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="FR2" s="1" t="s">
+      <c r="FS2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="FS2" s="1" t="s">
+      <c r="FT2" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="FT2" s="1" t="s">
+      <c r="FU2" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="FU2" s="1" t="s">
+      <c r="FV2" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="FV2" s="1" t="s">
+      <c r="FW2" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="FW2" s="1" t="s">
+      <c r="FX2" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="FX2" s="1" t="s">
+      <c r="FY2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="FY2" s="1" t="s">
+      <c r="FZ2" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="FZ2" s="1" t="s">
+      <c r="GA2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="GA2" s="1" t="s">
+      <c r="GB2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="GB2" s="1" t="s">
+      <c r="GC2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="GC2" s="1" t="s">
+      <c r="GD2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="GD2" s="1" t="s">
+      <c r="GE2" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="GE2" s="1" t="s">
+      <c r="GF2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="GF2" s="1" t="s">
+      <c r="GG2" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="GG2" s="1" t="s">
+      <c r="GH2" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="GH2" s="1" t="s">
+      <c r="GI2" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="GI2" s="1" t="s">
+      <c r="GJ2" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="GJ2" s="1" t="s">
+      <c r="GK2" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="GK2" s="1" t="s">
+      <c r="GL2" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="GL2" s="1" t="s">
+      <c r="GM2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="GM2" s="1" t="s">
+      <c r="GN2" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="GN2" s="1" t="s">
+      <c r="GO2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="GO2" s="1" t="s">
+      <c r="GP2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="GP2" s="1" t="s">
+      <c r="GQ2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="GQ2" s="1" t="s">
+      <c r="GR2" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="GR2" s="1" t="s">
+      <c r="GS2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="GS2" s="1" t="s">
+      <c r="GT2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="GT2" s="1" t="s">
+      <c r="GU2" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="GU2" s="1" t="s">
+      <c r="GV2" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="GV2" s="1" t="s">
+      <c r="GW2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="GW2" s="1" t="s">
+      <c r="GX2" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="GX2" s="1" t="s">
+      <c r="GY2" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="GY2" s="1" t="s">
+      <c r="GZ2" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="GZ2" s="1" t="s">
+      <c r="HA2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="HA2" s="1" t="s">
+      <c r="HB2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="HB2" s="1" t="s">
+      <c r="HC2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="HC2" s="1" t="s">
+      <c r="HD2" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="HD2" s="1" t="s">
+      <c r="HE2" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="HE2" s="1" t="s">
+      <c r="HF2" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="HF2" s="1" t="s">
+      <c r="HG2" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="HG2" s="1" t="s">
+      <c r="HH2" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="HH2" s="1" t="s">
+      <c r="HI2" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="HI2" s="1" t="s">
+      <c r="HJ2" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="HJ2" s="1" t="s">
+      <c r="HK2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="HK2" s="1" t="s">
+      <c r="HL2" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="HL2" s="1" t="s">
+      <c r="HM2" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="HM2" s="1" t="s">
+      <c r="HN2" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="HN2" s="1" t="s">
+      <c r="HO2" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="HO2" s="1" t="s">
+      <c r="HP2" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="HP2" s="1" t="s">
+      <c r="HQ2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="HQ2" s="1" t="s">
+      <c r="HR2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="HR2" s="1" t="s">
+      <c r="HS2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="HS2" s="1" t="s">
+      <c r="HT2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="HT2" s="1" t="s">
+      <c r="HU2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="HU2" s="1" t="s">
+      <c r="HV2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="HV2" s="1" t="s">
+      <c r="HW2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="HW2" s="1" t="s">
+      <c r="HX2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="HX2" s="1" t="s">
+      <c r="HY2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="HY2" s="1" t="s">
+      <c r="HZ2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="HZ2" s="1" t="s">
+      <c r="IA2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="IA2" s="1" t="s">
+      <c r="IB2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="IB2" s="1" t="s">
+      <c r="IC2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="IC2" s="1" t="s">
+      <c r="ID2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="ID2" s="1" t="s">
+      <c r="IE2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="IE2" s="1" t="s">
+      <c r="IF2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="IF2" s="1" t="s">
+      <c r="IG2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="IG2" s="1" t="s">
+      <c r="IH2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="IH2" s="1" t="s">
+      <c r="II2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="II2" s="1" t="s">
+      <c r="IJ2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="IJ2" s="1" t="s">
+      <c r="IK2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="IK2" s="1" t="s">
+      <c r="IL2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="IL2" s="1" t="s">
+      <c r="IM2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="IM2" s="1" t="s">
+      <c r="IN2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="IN2" s="1" t="s">
+      <c r="IO2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="IO2" s="1" t="s">
+      <c r="IP2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="IP2" s="1" t="s">
+      <c r="IQ2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="IQ2" s="1" t="s">
+      <c r="IR2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="IR2" s="1" t="s">
+      <c r="IS2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="IS2" s="1" t="s">
+      <c r="IT2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="IT2" s="1" t="s">
+      <c r="IU2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="IU2" s="1" t="s">
+      <c r="IV2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="IV2" s="1" t="s">
+      <c r="IW2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="IW2" s="1" t="s">
+      <c r="IX2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="IX2" s="1" t="s">
+      <c r="IY2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="IY2" s="1" t="s">
+      <c r="IZ2" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="IZ2" s="1" t="s">
+      <c r="JA2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="JA2" s="1" t="s">
+      <c r="JB2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="JB2" s="1" t="s">
+      <c r="JC2" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="JC2" s="1" t="s">
+      <c r="JD2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="JD2" s="1" t="s">
+      <c r="JE2" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="JE2" s="1" t="s">
+      <c r="JF2" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="JF2" s="1" t="s">
+      <c r="JG2" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="JG2" s="1" t="s">
+      <c r="JH2" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="JH2" s="1" t="s">
+      <c r="JI2" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="JI2" s="1" t="s">
+      <c r="JJ2" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="JJ2" s="1" t="s">
+      <c r="JK2" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="JK2" s="1" t="s">
+      <c r="JL2" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="JL2" s="1" t="s">
+      <c r="JM2" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="JM2" s="1" t="s">
+      <c r="JN2" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="JN2" s="1" t="s">
+      <c r="JO2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="JO2" s="1" t="s">
+      <c r="JP2" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="JP2" s="1" t="s">
+      <c r="JQ2" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="JQ2" s="1" t="s">
+      <c r="JR2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="JR2" s="1" t="s">
+      <c r="JS2" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:278" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:279" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3">
         <v>2025</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>278</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>279</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>280</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>281</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>282</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>283</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>284</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>285</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>286</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>287</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>288</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>289</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>290</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>291</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>292</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>293</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>294</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>295</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>296</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>297</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>298</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>299</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>293</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>294</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>300</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>296</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>301</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>302</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>303</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>293</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>304</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>305</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>306</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>307</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>298</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>308</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>309</v>
       </c>
-      <c r="AM3">
+      <c r="AN3">
         <v>1</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AO3" t="s">
         <v>293</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AP3" t="s">
         <v>304</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AQ3" t="s">
         <v>310</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AR3" t="s">
         <v>306</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AS3" t="s">
         <v>311</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AT3" t="s">
         <v>312</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AU3" t="s">
         <v>313</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AV3" t="s">
         <v>314</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AW3" t="s">
         <v>315</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>316</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>317</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="AZ3" t="s">
         <v>318</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BA3" t="s">
         <v>319</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BB3" t="s">
         <v>320</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BC3" t="s">
         <v>321</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BD3" t="s">
         <v>322</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
         <v>323</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BF3" t="s">
         <v>324</v>
       </c>
-      <c r="BF3" t="s">
+      <c r="BG3" t="s">
         <v>325</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BH3" t="s">
         <v>326</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BI3" t="s">
         <v>327</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BJ3" t="s">
         <v>328</v>
       </c>
-      <c r="BJ3" t="s">
+      <c r="BK3" t="s">
         <v>329</v>
       </c>
-      <c r="BK3" t="s">
+      <c r="BL3" t="s">
         <v>330</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BM3" t="s">
         <v>331</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BN3" t="s">
         <v>332</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BO3" t="s">
         <v>333</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BP3" t="s">
         <v>293</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BQ3" t="s">
         <v>334</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BR3" t="s">
         <v>335</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BS3" t="s">
         <v>336</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BT3" t="s">
         <v>337</v>
       </c>
-      <c r="BT3" t="s">
+      <c r="BU3" t="s">
         <v>336</v>
       </c>
-      <c r="BU3" t="s">
+      <c r="BV3" t="s">
         <v>338</v>
       </c>
-      <c r="BV3" t="s">
+      <c r="BW3" t="s">
         <v>339</v>
       </c>
-      <c r="BW3" t="s">
+      <c r="BX3" t="s">
         <v>340</v>
       </c>
-      <c r="BX3" t="s">
+      <c r="BY3" t="s">
         <v>341</v>
       </c>
-      <c r="BY3" t="s">
+      <c r="BZ3" t="s">
         <v>342</v>
       </c>
-      <c r="BZ3" t="s">
+      <c r="CA3" t="s">
         <v>343</v>
       </c>
-      <c r="CA3" t="s">
+      <c r="CB3" t="s">
         <v>342</v>
       </c>
-      <c r="CB3" t="s">
+      <c r="CC3" t="s">
         <v>344</v>
       </c>
-      <c r="CC3" t="s">
+      <c r="CD3" t="s">
         <v>345</v>
-      </c>
-      <c r="CD3">
-        <v>5</v>
       </c>
       <c r="CE3">
         <v>5</v>
       </c>
       <c r="CF3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CG3">
         <v>6</v>
       </c>
       <c r="CH3">
+        <v>6</v>
+      </c>
+      <c r="CI3">
         <v>7</v>
-      </c>
-      <c r="CI3">
-        <v>6</v>
       </c>
       <c r="CJ3">
         <v>6</v>
@@ -2583,43 +2595,43 @@
         <v>6</v>
       </c>
       <c r="CL3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CM3">
         <v>8</v>
       </c>
       <c r="CN3">
+        <v>8</v>
+      </c>
+      <c r="CO3">
         <v>6</v>
       </c>
-      <c r="CO3">
+      <c r="CP3">
         <v>8</v>
       </c>
-      <c r="CP3">
+      <c r="CQ3">
         <v>77</v>
       </c>
-      <c r="CQ3">
+      <c r="CR3">
         <v>5</v>
       </c>
-      <c r="CR3">
+      <c r="CS3">
         <v>4</v>
-      </c>
-      <c r="CS3">
-        <v>6</v>
       </c>
       <c r="CT3">
         <v>6</v>
       </c>
       <c r="CU3">
+        <v>6</v>
+      </c>
+      <c r="CV3">
         <v>8</v>
       </c>
-      <c r="CV3">
+      <c r="CW3">
         <v>5</v>
       </c>
-      <c r="CW3">
+      <c r="CX3">
         <v>6</v>
-      </c>
-      <c r="CX3">
-        <v>8</v>
       </c>
       <c r="CY3">
         <v>8</v>
@@ -2631,13 +2643,13 @@
         <v>8</v>
       </c>
       <c r="DB3">
+        <v>8</v>
+      </c>
+      <c r="DC3">
         <v>10</v>
       </c>
-      <c r="DC3">
+      <c r="DD3">
         <v>82</v>
-      </c>
-      <c r="ED3">
-        <v>5</v>
       </c>
       <c r="EE3">
         <v>5</v>
@@ -2649,16 +2661,16 @@
         <v>5</v>
       </c>
       <c r="EH3">
+        <v>5</v>
+      </c>
+      <c r="EI3">
         <v>7</v>
       </c>
-      <c r="EI3">
+      <c r="EJ3">
         <v>4</v>
       </c>
-      <c r="EJ3">
+      <c r="EK3">
         <v>6</v>
-      </c>
-      <c r="EK3">
-        <v>9</v>
       </c>
       <c r="EL3">
         <v>9</v>
@@ -2667,19 +2679,19 @@
         <v>9</v>
       </c>
       <c r="EN3">
+        <v>9</v>
+      </c>
+      <c r="EO3">
         <v>8</v>
       </c>
-      <c r="EO3">
+      <c r="EP3">
         <v>9</v>
       </c>
-      <c r="EP3">
+      <c r="EQ3">
         <v>81</v>
       </c>
-      <c r="FD3">
+      <c r="FE3">
         <v>5</v>
-      </c>
-      <c r="FE3">
-        <v>4</v>
       </c>
       <c r="FF3">
         <v>4</v>
@@ -2688,49 +2700,49 @@
         <v>4</v>
       </c>
       <c r="FH3">
+        <v>4</v>
+      </c>
+      <c r="FI3">
         <v>5</v>
       </c>
-      <c r="FI3">
+      <c r="FJ3">
         <v>4</v>
       </c>
-      <c r="FJ3">
+      <c r="FK3">
         <v>5</v>
       </c>
-      <c r="FK3">
+      <c r="FL3">
         <v>7</v>
       </c>
-      <c r="FL3">
+      <c r="FM3">
         <v>8</v>
       </c>
-      <c r="FM3">
+      <c r="FN3">
         <v>9</v>
       </c>
-      <c r="FN3">
+      <c r="FO3">
         <v>6</v>
       </c>
-      <c r="FO3">
+      <c r="FP3">
         <v>9</v>
       </c>
-      <c r="FP3">
+      <c r="FQ3">
         <v>70</v>
-      </c>
-      <c r="FQ3">
-        <v>4000</v>
       </c>
       <c r="FR3">
         <v>4000</v>
       </c>
       <c r="FS3">
-        <v>4800</v>
+        <v>4000</v>
       </c>
       <c r="FT3">
         <v>4800</v>
       </c>
       <c r="FU3">
+        <v>4800</v>
+      </c>
+      <c r="FV3">
         <v>5600</v>
-      </c>
-      <c r="FV3">
-        <v>4800</v>
       </c>
       <c r="FW3">
         <v>4800</v>
@@ -2739,43 +2751,43 @@
         <v>4800</v>
       </c>
       <c r="FY3">
-        <v>6400</v>
+        <v>4800</v>
       </c>
       <c r="FZ3">
         <v>6400</v>
       </c>
       <c r="GA3">
+        <v>6400</v>
+      </c>
+      <c r="GB3">
         <v>4800</v>
       </c>
-      <c r="GB3">
+      <c r="GC3">
         <v>6400</v>
       </c>
-      <c r="GC3">
+      <c r="GD3">
         <v>61600</v>
       </c>
-      <c r="GD3">
+      <c r="GE3">
         <v>4000</v>
       </c>
-      <c r="GE3">
+      <c r="GF3">
         <v>3200</v>
-      </c>
-      <c r="GF3">
-        <v>4800</v>
       </c>
       <c r="GG3">
         <v>4800</v>
       </c>
       <c r="GH3">
+        <v>4800</v>
+      </c>
+      <c r="GI3">
         <v>6400</v>
       </c>
-      <c r="GI3">
+      <c r="GJ3">
         <v>4000</v>
       </c>
-      <c r="GJ3">
+      <c r="GK3">
         <v>4800</v>
-      </c>
-      <c r="GK3">
-        <v>6400</v>
       </c>
       <c r="GL3">
         <v>6400</v>
@@ -2787,34 +2799,34 @@
         <v>6400</v>
       </c>
       <c r="GO3">
+        <v>6400</v>
+      </c>
+      <c r="GP3">
         <v>8000</v>
       </c>
-      <c r="GP3">
+      <c r="GQ3">
         <v>65600</v>
       </c>
-      <c r="GQ3">
+      <c r="GR3">
         <v>3920</v>
       </c>
-      <c r="GR3">
+      <c r="GS3">
         <v>3136</v>
-      </c>
-      <c r="GS3">
-        <v>4704</v>
       </c>
       <c r="GT3">
         <v>4704</v>
       </c>
       <c r="GU3">
+        <v>4704</v>
+      </c>
+      <c r="GV3">
         <v>6272</v>
       </c>
-      <c r="GV3">
+      <c r="GW3">
         <v>3920</v>
       </c>
-      <c r="GW3">
+      <c r="GX3">
         <v>4704</v>
-      </c>
-      <c r="GX3">
-        <v>6272</v>
       </c>
       <c r="GY3">
         <v>6272</v>
@@ -2826,13 +2838,13 @@
         <v>6272</v>
       </c>
       <c r="HB3">
+        <v>6272</v>
+      </c>
+      <c r="HC3">
         <v>7840</v>
       </c>
-      <c r="HC3">
+      <c r="HD3">
         <v>64288</v>
-      </c>
-      <c r="HD3">
-        <v>600</v>
       </c>
       <c r="HE3">
         <v>600</v>
@@ -2844,16 +2856,16 @@
         <v>600</v>
       </c>
       <c r="HH3">
+        <v>600</v>
+      </c>
+      <c r="HI3">
         <v>840</v>
       </c>
-      <c r="HI3">
+      <c r="HJ3">
         <v>480</v>
       </c>
-      <c r="HJ3">
+      <c r="HK3">
         <v>720</v>
-      </c>
-      <c r="HK3">
-        <v>1080</v>
       </c>
       <c r="HL3">
         <v>1080</v>
@@ -2862,16 +2874,16 @@
         <v>1080</v>
       </c>
       <c r="HN3">
+        <v>1080</v>
+      </c>
+      <c r="HO3">
         <v>960</v>
       </c>
-      <c r="HO3">
+      <c r="HP3">
         <v>1080</v>
       </c>
-      <c r="HP3">
+      <c r="HQ3">
         <v>9720</v>
-      </c>
-      <c r="HQ3">
-        <v>4000</v>
       </c>
       <c r="HR3">
         <v>4000</v>
@@ -2883,16 +2895,16 @@
         <v>4000</v>
       </c>
       <c r="HU3">
+        <v>4000</v>
+      </c>
+      <c r="HV3">
         <v>5600</v>
       </c>
-      <c r="HV3">
+      <c r="HW3">
         <v>3200</v>
       </c>
-      <c r="HW3">
+      <c r="HX3">
         <v>4800</v>
-      </c>
-      <c r="HX3">
-        <v>7200</v>
       </c>
       <c r="HY3">
         <v>7200</v>
@@ -2901,19 +2913,19 @@
         <v>7200</v>
       </c>
       <c r="IA3">
+        <v>7200</v>
+      </c>
+      <c r="IB3">
         <v>6400</v>
       </c>
-      <c r="IB3">
+      <c r="IC3">
         <v>7200</v>
       </c>
-      <c r="IC3">
+      <c r="ID3">
         <v>64800</v>
       </c>
-      <c r="IQ3">
+      <c r="IR3">
         <v>4000</v>
-      </c>
-      <c r="IR3">
-        <v>3200</v>
       </c>
       <c r="IS3">
         <v>3200</v>
@@ -2922,44 +2934,47 @@
         <v>3200</v>
       </c>
       <c r="IU3">
+        <v>3200</v>
+      </c>
+      <c r="IV3">
         <v>4000</v>
       </c>
-      <c r="IV3">
+      <c r="IW3">
         <v>3200</v>
       </c>
-      <c r="IW3">
+      <c r="IX3">
         <v>4000</v>
       </c>
-      <c r="IX3">
+      <c r="IY3">
         <v>5600</v>
       </c>
-      <c r="IY3">
+      <c r="IZ3">
         <v>6400</v>
       </c>
-      <c r="IZ3">
+      <c r="JA3">
         <v>7200</v>
       </c>
-      <c r="JA3">
+      <c r="JB3">
         <v>4800</v>
       </c>
-      <c r="JB3">
+      <c r="JC3">
         <v>7200</v>
       </c>
-      <c r="JC3">
+      <c r="JD3">
         <v>56000</v>
       </c>
-      <c r="JP3" t="s">
+      <c r="JQ3" t="s">
         <v>346</v>
-      </c>
-      <c r="JQ3" t="s">
-        <v>336</v>
       </c>
       <c r="JR3" t="s">
         <v>336</v>
       </c>
+      <c r="JS3" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:JR3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:JS3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>